--- a/outputs/q4/q4_atomic_components.xlsx
+++ b/outputs/q4/q4_atomic_components.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'transport_components'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'strict_components'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'relay_bindings'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'relay_bindings'!$A$1:$C$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -507,24 +507,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009</t>
+          <t>S002,S003,S004,S005,S007,S009,S015</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Q2-002,Q2-005,Q2-006,Q2-010,Q2-017,Q2-018,Q2-023,Q2-026</t>
+          <t>Q2-004,Q2-007,Q2-008,Q2-010,Q2-011,Q2-012,Q2-014,Q2-015,Q2-018,Q2-019,Q2-021,Q2-023,Q2-026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04,Q3-R05</t>
+          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>224</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4">
@@ -535,24 +535,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S003,S007,S011,S014,S015</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-003,Q2-007,Q2-011,Q2-013,Q2-014,Q2-016,Q2-021</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Q3-R01,Q3-R02,Q3-R04,Q3-R05</t>
-        </is>
-      </c>
+          <t>Q2-001,Q2-002,Q2-017</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -563,20 +559,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Q2-008,Q2-020,Q2-022</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Q2-003,Q2-006</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Q3-R03,Q3-R04</t>
+        </is>
+      </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6">
@@ -587,24 +587,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S010,S012,S013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Q2-015,Q2-019</t>
+          <t>Q2-016,Q2-024,Q2-025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Q3-R04,Q3-R05</t>
+          <t>Q3-R02,Q3-R03</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -615,24 +615,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S010,S012,S013</t>
+          <t>S011,S014</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Q2-004,Q2-009,Q2-025</t>
+          <t>Q2-009,Q2-013,Q2-020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Q3-R02,Q3-R03</t>
+          <t>Q3-R02</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -703,7 +703,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Q2-012,Q2-024</t>
+          <t>Q2-005,Q2-022</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-006,Q2-007,Q2-009,Q2-010,Q2-011,Q2-013,Q2-014,Q2-015,Q2-016,Q2-017,Q2-018,Q2-019,Q2-021,Q2-023,Q2-025,Q2-026</t>
+          <t>Q2-003,Q2-004,Q2-006,Q2-007,Q2-008,Q2-009,Q2-010,Q2-011,Q2-012,Q2-013,Q2-014,Q2-015,Q2-016,Q2-018,Q2-019,Q2-020,Q2-021,Q2-023,Q2-024,Q2-025,Q2-026</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04,Q3-R05</t>
+          <t>Q3-R01,Q3-R02,Q3-R03,Q3-R04</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -755,7 +755,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Q2-008,Q2-020,Q2-022</t>
+          <t>Q2-001,Q2-002,Q2-017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -811,12 +811,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q2-007,Q2-013,Q2-016,Q2-017</t>
+          <t>Q2-014,Q2-019,Q2-026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S002,S003,S007,S015</t>
+          <t>S003,S007,S015</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q2-001,Q2-002,Q2-003,Q2-004,Q2-005,Q2-009,Q2-017,Q2-025</t>
+          <t>Q2-009,Q2-012,Q2-015,Q2-016,Q2-020,Q2-021,Q2-024,Q2-025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2-002,Q2-010,Q2-018,Q2-023,Q2-025,Q2-026</t>
+          <t>Q2-006,Q2-007,Q2-011,Q2-015,Q2-018,Q2-023,Q2-025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S002,S004,S005,S009,S012,S013</t>
+          <t>S002,S004,S005,S007,S008,S009,S012,S013</t>
         </is>
       </c>
     </row>
@@ -862,34 +862,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q2-006,Q2-010,Q2-011,Q2-014,Q2-015,Q2-018,Q2-019,Q2-021</t>
+          <t>Q2-003,Q2-004,Q2-006,Q2-007,Q2-008,Q2-010,Q2-018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S002,S003,S004,S005,S007,S008,S009,S011,S015</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Q3-R05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Q2-006,Q2-014,Q2-015,Q2-019</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>S002,S007,S008,S009,S011</t>
+          <t>S003,S004,S005,S007,S008,S009,S015</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
+  <autoFilter ref="A1:C5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>